--- a/output/StructureDefinition-BRPlanoCuidados-1.0.xlsx
+++ b/output/StructureDefinition-BRPlanoCuidados-1.0.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3463" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3461" uniqueCount="614">
   <si>
     <t>Property</t>
   </si>
@@ -816,6 +816,15 @@
     <t>gender</t>
   </si>
   <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>Sexo biológico obtido por meio de exame clínico ou de outros métodos diagnósticos referente ao indivíduo da hipótese de impossibilidade de identificação.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRSexo-1.0</t>
+  </si>
+  <si>
     <t>CarePlan.subject.extension:unidentifiedPatient.extension:gender.id</t>
   </si>
   <si>
@@ -868,6 +877,12 @@
   </si>
   <si>
     <t>birthYear</t>
+  </si>
+  <si>
+    <t>Ano de nascimento estimado</t>
+  </si>
+  <si>
+    <t>Estimativa do ano de nascimento por meio de observação direta da idade do indivíduo na hipótese de impossibilidade de identificação..</t>
   </si>
   <si>
     <t>CarePlan.subject.extension:unidentifiedPatient.extension:birthYear.id</t>
@@ -890,6 +905,15 @@
   </si>
   <si>
     <t>reason</t>
+  </si>
+  <si>
+    <t>Justificativa da impossibilidade de identificação do indivíduo</t>
+  </si>
+  <si>
+    <t>Razão pela qual não foi possível obter os dados de identificação do indivíduo no contato assistencial.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRJustificativaIndividuoNaoIdentificado-1.0</t>
   </si>
   <si>
     <t>CarePlan.subject.extension:unidentifiedPatient.extension:reason.id</t>
@@ -1850,6 +1874,10 @@
   </si>
   <si>
     <t>Allows rough dose checking.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP][classCode=SBADM].doseQuantity</t>
@@ -2244,7 +2272,7 @@
     <col min="23" max="23" width="16.40625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="15.85546875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="140.19921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.21875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.20703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.1171875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.56640625" customWidth="true" bestFit="true"/>
@@ -5373,10 +5401,10 @@
         <v>134</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5403,13 +5431,11 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>81</v>
+        <v>258</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -5456,10 +5482,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5568,10 +5594,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5600,7 +5626,7 @@
         <v>135</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>137</v>
@@ -5682,10 +5708,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5711,13 +5737,13 @@
         <v>102</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5767,7 +5793,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>89</v>
@@ -5796,10 +5822,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5825,10 +5851,10 @@
         <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5879,7 +5905,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5908,13 +5934,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>252</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>81</v>
@@ -5939,10 +5965,10 @@
         <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>238</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>239</v>
+        <v>278</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6022,10 +6048,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6134,10 +6160,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6166,7 +6192,7 @@
         <v>135</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>137</v>
@@ -6248,10 +6274,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6277,13 +6303,13 @@
         <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6291,7 +6317,7 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>81</v>
@@ -6333,7 +6359,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>89</v>
@@ -6362,10 +6388,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6388,13 +6414,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6445,7 +6471,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6474,13 +6500,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>252</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>81</v>
@@ -6505,10 +6531,10 @@
         <v>134</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>238</v>
+        <v>286</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>239</v>
+        <v>287</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6535,13 +6561,11 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6588,10 +6612,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6700,10 +6724,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6732,7 +6756,7 @@
         <v>135</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>137</v>
@@ -6814,10 +6838,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6843,13 +6867,13 @@
         <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6857,7 +6881,7 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>81</v>
@@ -6899,7 +6923,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>89</v>
@@ -6928,10 +6952,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6957,10 +6981,10 @@
         <v>205</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7011,7 +7035,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7040,10 +7064,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7069,13 +7093,13 @@
         <v>102</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7083,7 +7107,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>81</v>
@@ -7125,7 +7149,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>89</v>
@@ -7154,10 +7178,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7180,13 +7204,13 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7237,7 +7261,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7266,10 +7290,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7295,13 +7319,13 @@
         <v>215</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7351,7 +7375,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7360,7 +7384,7 @@
         <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>100</v>
@@ -7380,10 +7404,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7409,13 +7433,13 @@
         <v>102</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7441,13 +7465,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7465,7 +7489,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7494,10 +7518,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7523,13 +7547,13 @@
         <v>146</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7579,7 +7603,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7597,7 +7621,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7608,10 +7632,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7720,10 +7744,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7752,7 +7776,7 @@
         <v>135</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>137</v>
@@ -7834,10 +7858,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7863,16 +7887,16 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -7900,10 +7924,10 @@
         <v>189</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7921,7 +7945,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7939,7 +7963,7 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
@@ -7950,10 +7974,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7979,16 +8003,16 @@
         <v>205</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8013,13 +8037,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8037,7 +8061,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8055,21 +8079,21 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8095,16 +8119,16 @@
         <v>102</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8117,7 +8141,7 @@
         <v>81</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>81</v>
@@ -8153,7 +8177,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8171,21 +8195,21 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8211,13 +8235,13 @@
         <v>215</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8231,7 +8255,7 @@
         <v>81</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>81</v>
@@ -8267,7 +8291,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8285,21 +8309,21 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8322,13 +8346,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8379,7 +8403,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8397,21 +8421,21 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8434,16 +8458,16 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8493,7 +8517,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8511,21 +8535,21 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8551,13 +8575,13 @@
         <v>215</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8607,7 +8631,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8636,10 +8660,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8662,16 +8686,16 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8721,7 +8745,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8736,28 +8760,28 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8776,19 +8800,19 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8837,7 +8861,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8852,28 +8876,28 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8892,13 +8916,13 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8949,7 +8973,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8964,13 +8988,13 @@
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -8978,10 +9002,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9004,16 +9028,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9063,7 +9087,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9078,13 +9102,13 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
@@ -9092,10 +9116,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9118,16 +9142,16 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9177,7 +9201,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9206,10 +9230,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9232,17 +9256,17 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9291,7 +9315,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9306,13 +9330,13 @@
         <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -9320,10 +9344,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9346,19 +9370,19 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9407,7 +9431,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9422,24 +9446,24 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9462,19 +9486,19 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9523,7 +9547,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9538,7 +9562,7 @@
         <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>81</v>
@@ -9552,10 +9576,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9578,19 +9602,19 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -9639,7 +9663,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9657,21 +9681,21 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9694,17 +9718,17 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -9753,7 +9777,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9765,13 +9789,13 @@
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -9782,10 +9806,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9894,10 +9918,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9926,7 +9950,7 @@
         <v>135</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>137</v>
@@ -10008,14 +10032,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10037,10 +10061,10 @@
         <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>137</v>
@@ -10095,7 +10119,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10124,10 +10148,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10153,13 +10177,13 @@
         <v>205</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10188,10 +10212,10 @@
         <v>210</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>81</v>
@@ -10209,7 +10233,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10238,10 +10262,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10264,19 +10288,19 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -10325,7 +10349,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10340,10 +10364,10 @@
         <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -10354,10 +10378,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10380,19 +10404,19 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10441,7 +10465,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10459,21 +10483,21 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10496,19 +10520,19 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>81</v>
@@ -10557,7 +10581,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10566,16 +10590,16 @@
         <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -10586,10 +10610,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10612,17 +10636,17 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -10671,7 +10695,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10680,7 +10704,7 @@
         <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>100</v>
@@ -10689,7 +10713,7 @@
         <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -10700,10 +10724,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10812,10 +10836,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10844,7 +10868,7 @@
         <v>135</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>137</v>
@@ -10926,14 +10950,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10955,10 +10979,10 @@
         <v>134</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>137</v>
@@ -11013,7 +11037,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11042,10 +11066,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11071,14 +11095,14 @@
         <v>108</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -11106,10 +11130,10 @@
         <v>189</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -11127,7 +11151,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11145,7 +11169,7 @@
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>
@@ -11156,10 +11180,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11182,17 +11206,17 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>157</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
@@ -11241,7 +11265,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11270,10 +11294,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11302,13 +11326,13 @@
         <v>162</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>164</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -11357,7 +11381,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11386,10 +11410,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11415,16 +11439,16 @@
         <v>205</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>81</v>
@@ -11452,10 +11476,10 @@
         <v>210</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>81</v>
@@ -11473,7 +11497,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11488,24 +11512,24 @@
         <v>100</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11531,13 +11555,13 @@
         <v>205</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11566,10 +11590,10 @@
         <v>210</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>81</v>
@@ -11587,7 +11611,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11602,7 +11626,7 @@
         <v>100</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>81</v>
@@ -11616,10 +11640,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11642,16 +11666,16 @@
         <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11701,7 +11725,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11716,7 +11740,7 @@
         <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>81</v>
@@ -11730,10 +11754,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11756,17 +11780,17 @@
         <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -11815,7 +11839,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11833,7 +11857,7 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
@@ -11844,10 +11868,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11873,16 +11897,16 @@
         <v>108</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -11910,10 +11934,10 @@
         <v>189</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>81</v>
@@ -11931,7 +11955,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>89</v>
@@ -11946,24 +11970,24 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11989,13 +12013,13 @@
         <v>205</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12045,7 +12069,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12060,7 +12084,7 @@
         <v>100</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>81</v>
@@ -12074,10 +12098,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12100,25 +12124,25 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q87" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="R87" t="s" s="2">
         <v>81</v>
@@ -12163,7 +12187,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12178,10 +12202,10 @@
         <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
@@ -12192,10 +12216,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12218,17 +12242,17 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
@@ -12277,7 +12301,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12292,24 +12316,24 @@
         <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12332,19 +12356,19 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -12393,7 +12417,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12411,21 +12435,21 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12448,19 +12472,19 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -12509,7 +12533,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12524,24 +12548,24 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12564,13 +12588,13 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12600,10 +12624,10 @@
         <v>210</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -12621,7 +12645,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12639,25 +12663,25 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12676,17 +12700,17 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -12735,7 +12759,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12747,27 +12771,27 @@
         <v>81</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>100</v>
+        <v>597</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>590</v>
+        <v>599</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12790,13 +12814,13 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12847,7 +12871,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12859,27 +12883,27 @@
         <v>81</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>100</v>
+        <v>597</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>595</v>
+        <v>604</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12905,10 +12929,10 @@
         <v>215</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12959,7 +12983,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12977,21 +13001,21 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13014,17 +13038,17 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -13073,7 +13097,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13088,16 +13112,16 @@
         <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
